--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD1" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAMPLE" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUB5" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEP LEARNING" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPILER DESIGN1" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1384,6 +1386,274 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>VISHNU</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24CS21</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>49.74%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BAN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24CSD78</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>96.23%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -23,6 +23,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUB5" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEP LEARNING" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPILER DESIGN1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DBMS21" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DBMS22" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD2" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPILER_DESIGN" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD3" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD4" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPILER_DESIGN_SUB" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1654,6 +1662,362 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sample Student Answer Sheet</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Compiler Design Random Student Long Answers No Cover</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>10.74%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Compiler Design University Key Minimal</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>8.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sample Student Answer Sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1753,6 +2117,656 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>64.76%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RAJU</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24CS010</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RAJU</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>24CS010</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RAJU</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24B11CS409</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RAJU</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24CS90</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Compiler Design University Key Minimal</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>8.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sample Student Answer Sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>65.38%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Register No.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SRUJITH</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24B11CS137</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>56.54%</t>
         </is>
       </c>
     </row>
